--- a/examples/lab_forms_excel/xlsx/staircase.xlsx
+++ b/examples/lab_forms_excel/xlsx/staircase.xlsx
@@ -37,7 +37,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Источник: photo_7_staircase_pretest3_2026-07-10.xlsx</x:t>
+    Source: photo_7_staircase_pretest3_2026-07-10.xlsx</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -47,7 +47,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Порядковый номер. Формула ROW()-6 пересчитывает нумерацию при вставке и удалении строк данных.</x:t>
+    Sequential ID. The ROW()-6 formula updates numbering when data rows are inserted or deleted.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -57,7 +57,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    L1: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
+    L1: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -67,7 +67,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    L2: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
+    L2: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -77,7 +77,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    L3: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
+    L3: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -87,7 +87,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    L4: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
+    L4: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -97,7 +97,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    L5: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
+    L5: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -107,7 +107,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    L6: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
+    L6: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -117,7 +117,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    L7: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
+    L7: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -127,7 +127,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    L drop: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
+    L drop: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -137,7 +137,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    R1: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
+    R1: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -147,7 +147,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    R2: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
+    R2: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -157,7 +157,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    R3: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
+    R3: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -167,7 +167,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    R4: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
+    R4: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -177,7 +177,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    R5: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
+    R5: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -187,7 +187,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    R6: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
+    R6: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -197,7 +197,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    R7: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
+    R7: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -207,7 +207,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    R drop: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
+    R drop: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -217,7 +217,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Примечание к животному; переносится как текст.</x:t>
+    Animal notes; recognized and exported as text.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -592,61 +592,61 @@
 <file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
   <xltc:threadedComment ref="A1" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{0F3D4710-B64B-432C-BA81-7AC57ACF78A3}">
-    <xltc:text>Источник: photo_7_staircase_pretest3_2026-07-10.xlsx</xltc:text>
+    <xltc:text>Source: photo_7_staircase_pretest3_2026-07-10.xlsx</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="A6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{9F777F4B-2019-4515-AF3F-4F8E783E8AB2}">
-    <xltc:text>Порядковый номер. Формула ROW()-6 пересчитывает нумерацию при вставке и удалении строк данных.</xltc:text>
+    <xltc:text>Sequential ID. The ROW()-6 formula updates numbering when data rows are inserted or deleted.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="B6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{527B3052-6982-4281-B9EF-6164670D3F4B}">
-    <xltc:text>L1: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
+    <xltc:text>L1: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="C6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{1CE2E96D-78FE-48AC-AD2C-8EA2548F19BF}">
-    <xltc:text>L2: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
+    <xltc:text>L2: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="D6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{31AB3077-1122-41C3-B4EA-F380167F2E91}">
-    <xltc:text>L3: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
+    <xltc:text>L3: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="E6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{3AA51F2E-EB71-4050-8D15-9385F7ED4544}">
-    <xltc:text>L4: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
+    <xltc:text>L4: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="F6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{81B1C047-CA93-4FC4-AC68-0DCA9C79578C}">
-    <xltc:text>L5: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
+    <xltc:text>L5: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="G6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{54FABE4D-4773-4EDA-947D-D4D68927785B}">
-    <xltc:text>L6: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
+    <xltc:text>L6: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="H6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{CD92EDC1-D4A4-4194-AC71-3C3C6FBAB430}">
-    <xltc:text>L7: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
+    <xltc:text>L7: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="I6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{9C7B6C63-503E-4130-AF4A-DCAD2D475427}">
-    <xltc:text>L drop: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
+    <xltc:text>L drop: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="J6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{99FA6B62-154A-4645-B276-A5BC597AF025}">
-    <xltc:text>R1: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
+    <xltc:text>R1: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="K6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{AAFF3A88-5EBD-4A34-95FE-C71898EB8E77}">
-    <xltc:text>R2: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
+    <xltc:text>R2: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="L6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{56D903A3-B6B5-4B5E-A702-51C703494F5B}">
-    <xltc:text>R3: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
+    <xltc:text>R3: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="M6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{969C4ACD-7614-4339-8E03-3D6764AE7A2C}">
-    <xltc:text>R4: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
+    <xltc:text>R4: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="N6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{42D7BCB1-5AA0-453A-8887-51D8459EAECB}">
-    <xltc:text>R5: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
+    <xltc:text>R5: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="O6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{E2BAAAB9-8026-4075-B583-D0AD1EE82885}">
-    <xltc:text>R6: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
+    <xltc:text>R6: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="P6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{70D79586-F82B-4079-B2CD-22AB49515D10}">
-    <xltc:text>R7: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
+    <xltc:text>R7: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="Q6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{3481868C-D411-4C0D-BC06-888CC5A2D361}">
-    <xltc:text>R drop: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
+    <xltc:text>R drop: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="R6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{7F659BAF-AF7E-4137-A74B-5DD5B95D7167}">
-    <xltc:text>Примечание к животному; переносится как текст.</xltc:text>
+    <xltc:text>Animal notes; recognized and exported as text.</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
 </file>

--- a/examples/lab_forms_excel/xlsx/staircase.xlsx
+++ b/examples/lab_forms_excel/xlsx/staircase.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staircase" sheetId="1" r:id="Ra08cd465f5e4417d"/>
-  </x:sheets>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="Staircase" sheetId="1" ns1:id="R28baae5e99e04f9a"/>
+  </sheets>
+</workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -37,7 +37,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Source: photo_7_staircase_pretest3_2026-07-10.xlsx</x:t>
+    Источник: photo_7_staircase_pretest3_2026-07-10.xlsx</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -47,7 +47,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Sequential ID. The ROW()-6 formula updates numbering when data rows are inserted or deleted.</x:t>
+    Порядковый номер. Формула ROW()-6 пересчитывает нумерацию при вставке и удалении строк данных.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -57,7 +57,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    L1: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
+    L1: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -67,7 +67,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    L2: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
+    L2: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -77,7 +77,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    L3: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
+    L3: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -87,7 +87,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    L4: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
+    L4: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -97,7 +97,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    L5: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
+    L5: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -107,7 +107,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    L6: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
+    L6: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -117,7 +117,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    L7: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
+    L7: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -127,7 +127,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    L drop: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
+    L drop: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -137,7 +137,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    R1: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
+    R1: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -147,7 +147,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    R2: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
+    R2: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -157,7 +157,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    R3: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
+    R3: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -167,7 +167,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    R4: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
+    R4: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -177,7 +177,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    R5: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
+    R5: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -187,7 +187,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    R6: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
+    R6: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -197,7 +197,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    R7: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
+    R7: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -207,7 +207,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    R drop: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</x:t>
+    R drop: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -217,7 +217,7 @@
           <x:t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Animal notes; recognized and exported as text.</x:t>
+    Примечание к животному; переносится как текст.</x:t>
         </x:r>
       </x:text>
     </x:comment>
@@ -285,7 +285,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="3">
+  <x:borders count="15">
     <x:border/>
     <x:border>
       <x:bottom style="thin">
@@ -306,11 +306,75 @@
         <x:color rgb="FF333333"/>
       </x:bottom>
     </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none"/>
+      <x:top style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:top style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:right style="none"/>
+      <x:top style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none"/>
+      <x:bottom style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:bottom style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:right style="none"/>
+      <x:bottom style="none"/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:right style="thin">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="20">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -357,6 +421,19 @@
     <x:xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -371,31 +448,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Animals_staircase" displayName="Animals_staircase" ref="A6:R26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <tableColumns count="18">
-    <tableColumn id="1" name="ID">
-      <calculatedColumnFormula>ROW()-6</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="2" name="L1"/>
-    <tableColumn id="3" name="L2"/>
-    <tableColumn id="4" name="L3"/>
-    <tableColumn id="5" name="L4"/>
-    <tableColumn id="6" name="L5"/>
-    <tableColumn id="7" name="L6"/>
-    <tableColumn id="8" name="L7"/>
-    <tableColumn id="9" name="L drop"/>
-    <tableColumn id="10" name="R1"/>
-    <tableColumn id="11" name="R2"/>
-    <tableColumn id="12" name="R3"/>
-    <tableColumn id="13" name="R4"/>
-    <tableColumn id="14" name="R5"/>
-    <tableColumn id="15" name="R6"/>
-    <tableColumn id="16" name="R7"/>
-    <tableColumn id="17" name="R drop"/>
-    <tableColumn id="18" name="Notes"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Animals_staircase" displayName="Animals_staircase" ref="A6:R26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="18">
+    <x:tableColumn id="1" name="ID">
+      <x:calculatedColumnFormula>ROW()-6</x:calculatedColumnFormula>
+    </x:tableColumn>
+    <x:tableColumn id="2" name="L1"/>
+    <x:tableColumn id="3" name="L2"/>
+    <x:tableColumn id="4" name="L3"/>
+    <x:tableColumn id="5" name="L4"/>
+    <x:tableColumn id="6" name="L5"/>
+    <x:tableColumn id="7" name="L6"/>
+    <x:tableColumn id="8" name="L7"/>
+    <x:tableColumn id="9" name="L drop"/>
+    <x:tableColumn id="10" name="R1"/>
+    <x:tableColumn id="11" name="R2"/>
+    <x:tableColumn id="12" name="R3"/>
+    <x:tableColumn id="13" name="R4"/>
+    <x:tableColumn id="14" name="R5"/>
+    <x:tableColumn id="15" name="R6"/>
+    <x:tableColumn id="16" name="R7"/>
+    <x:tableColumn id="17" name="R drop"/>
+    <x:tableColumn id="18" name="Notes"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -592,67 +669,67 @@
 <file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
   <xltc:threadedComment ref="A1" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{0F3D4710-B64B-432C-BA81-7AC57ACF78A3}">
-    <xltc:text>Source: photo_7_staircase_pretest3_2026-07-10.xlsx</xltc:text>
+    <xltc:text>Источник: photo_7_staircase_pretest3_2026-07-10.xlsx</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="A6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{9F777F4B-2019-4515-AF3F-4F8E783E8AB2}">
-    <xltc:text>Sequential ID. The ROW()-6 formula updates numbering when data rows are inserted or deleted.</xltc:text>
+    <xltc:text>Порядковый номер. Формула ROW()-6 пересчитывает нумерацию при вставке и удалении строк данных.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="B6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{527B3052-6982-4281-B9EF-6164670D3F4B}">
-    <xltc:text>L1: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
+    <xltc:text>L1: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="C6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{1CE2E96D-78FE-48AC-AD2C-8EA2548F19BF}">
-    <xltc:text>L2: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
+    <xltc:text>L2: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="D6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{31AB3077-1122-41C3-B4EA-F380167F2E91}">
-    <xltc:text>L3: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
+    <xltc:text>L3: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="E6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{3AA51F2E-EB71-4050-8D15-9385F7ED4544}">
-    <xltc:text>L4: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
+    <xltc:text>L4: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="F6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{81B1C047-CA93-4FC4-AC68-0DCA9C79578C}">
-    <xltc:text>L5: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
+    <xltc:text>L5: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="G6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{54FABE4D-4773-4EDA-947D-D4D68927785B}">
-    <xltc:text>L6: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
+    <xltc:text>L6: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="H6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{CD92EDC1-D4A4-4194-AC71-3C3C6FBAB430}">
-    <xltc:text>L7: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
+    <xltc:text>L7: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="I6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{9C7B6C63-503E-4130-AF4A-DCAD2D475427}">
-    <xltc:text>L drop: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
+    <xltc:text>L drop: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="J6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{99FA6B62-154A-4645-B276-A5BC597AF025}">
-    <xltc:text>R1: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
+    <xltc:text>R1: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="K6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{AAFF3A88-5EBD-4A34-95FE-C71898EB8E77}">
-    <xltc:text>R2: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
+    <xltc:text>R2: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="L6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{56D903A3-B6B5-4B5E-A702-51C703494F5B}">
-    <xltc:text>R3: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
+    <xltc:text>R3: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="M6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{969C4ACD-7614-4339-8E03-3D6764AE7A2C}">
-    <xltc:text>R4: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
+    <xltc:text>R4: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="N6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{42D7BCB1-5AA0-453A-8887-51D8459EAECB}">
-    <xltc:text>R5: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
+    <xltc:text>R5: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="O6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{E2BAAAB9-8026-4075-B583-D0AD1EE82885}">
-    <xltc:text>R6: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
+    <xltc:text>R6: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="P6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{70D79586-F82B-4079-B2CD-22AB49515D10}">
-    <xltc:text>R7: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
+    <xltc:text>R7: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="Q6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{3481868C-D411-4C0D-BC06-888CC5A2D361}">
-    <xltc:text>R drop: nonnegative integer. A blank cell means missing data, not zero. This rule covers every data row.</xltc:text>
+    <xltc:text>R drop: неотрицательное целое число. Пустая клетка означает пропуск, не ноль. Правило применяется ко всем строкам данных.</xltc:text>
   </xltc:threadedComment>
   <xltc:threadedComment ref="R6" dT="2026-09-14T15:06:57.638" personId="{3F3083CB-3F07-42B9-80F2-1D5038EB78B3}" id="{7F659BAF-AF7E-4137-A74B-5DD5B95D7167}">
-    <xltc:text>Animal notes; recognized and exported as text.</xltc:text>
+    <xltc:text>Примечание к животному; переносится как текст.</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1" autoPageBreaks="0"/>
   </sheetPr>
@@ -721,50 +798,50 @@
       <c r="R2" s="1"/>
     </row>
     <row r="3" ht="13" customHeight="1">
-      <c r="A3" s="3" t="str">
+      <c r="A3" s="27" t="str">
         <v>Date</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="3" t="str">
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="27" t="str">
         <v>Session</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="3" t="str">
+      <c r="E3" s="28"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="27" t="str">
         <v>Operator</v>
       </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="29"/>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
+      <c r="R3"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
+      <c r="A4" s="30"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="32"/>
+      <c r="M4"/>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+      <c r="R4"/>
     </row>
     <row r="5" ht="8" customHeight="1">
       <c r="A5" s="1"/>
@@ -1309,16 +1386,16 @@
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G3:R3"/>
-    <mergeCell ref="G4:R4"/>
+    <mergeCell ref="G3:L3"/>
+    <mergeCell ref="G4:L4"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <pageMargins left="0.3937" right="0.3937" top="0.3937" bottom="0.3937" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1" horizontalDpi="0" verticalDpi="0"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <headerFooter/>
-  <legacyDrawing r:id="Rde50bb368d784bb8"/>
+  <legacyDrawing ns1:id="R49e6ed87d5f14cd1"/>
   <tableParts count="1">
-    <tablePart r:id="R7e3cc2b1ddf34913"/>
+    <tablePart ns1:id="Rbcafb5b67b5943d8"/>
   </tableParts>
 </worksheet>
 </file>
--- a/examples/lab_forms_excel/xlsx/staircase.xlsx
+++ b/examples/lab_forms_excel/xlsx/staircase.xlsx
@@ -1389,9 +1389,9 @@
     <mergeCell ref="G3:L3"/>
     <mergeCell ref="G4:L4"/>
   </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <pageMargins left="0.3937" right="0.3937" top="0.3937" bottom="0.3937" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1" horizontalDpi="0" verticalDpi="0"/>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <headerFooter/>
   <legacyDrawing ns1:id="R49e6ed87d5f14cd1"/>
   <tableParts count="1">
